--- a/BARMM_EBDM_Consolidated_Dashboard_20260717.xlsx
+++ b/BARMM_EBDM_Consolidated_Dashboard_20260717.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3493612890174e52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province Summary" sheetId="2" r:id="R473379ade2ba4239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Benchmarks" sheetId="3" r:id="Rc8b0e347f3314b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipal Scores" sheetId="4" r:id="R0cbf7e42a79a4928"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Themes" sheetId="5" r:id="Rf253954957494791"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Coverage" sheetId="6" r:id="R4213188df8db40ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Notes" sheetId="7" r:id="Rc76a67933f874c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8dbcb9e1d7a54453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province Summary" sheetId="2" r:id="Rfb8a6650e1b64167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province Analysis" sheetId="3" r:id="R19f4f3d8b05d4bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Benchmarks" sheetId="4" r:id="R01593cfbb4c04efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipal Scores" sheetId="5" r:id="R3716c3ebb2584aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Themes" sheetId="6" r:id="Rbd2b6e4d69074ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Coverage" sheetId="7" r:id="R70109bed71534021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Notes" sheetId="8" r:id="Rb7d1060f300d4a05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1128,7 +1129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20bfa99f62df429e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e362375d37d49c8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1153,7 +1154,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6913949f55f42b2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6deddcfed61b494d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1178,7 +1179,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bc13a3c1aa24be4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R59631c3d2a134dff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1208,7 +1209,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b05f4e3006c4a49"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbfeb2b6081cc4f0d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1743,7 +1744,7 @@
     <x:mergeCell ref="A15:H15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48f14726d3c64809"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00978677da0d4786"/>
 </x:worksheet>
 </file>
 
@@ -2009,6 +2010,183 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="46.66999816894531" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="25.5" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Province Analysis</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Source-bounded province-by-province narrative analysis generated from the same dashboard data.</x:v>
+      </x:c>
+      <x:c r="B2" s="7"/>
+      <x:c r="C2" s="7"/>
+      <x:c r="D2" s="7"/>
+      <x:c r="E2" s="7"/>
+      <x:c r="F2" s="7"/>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="61" t="str">
+        <x:v>Province</x:v>
+      </x:c>
+      <x:c r="B4" s="62" t="str">
+        <x:v>Rank</x:v>
+      </x:c>
+      <x:c r="C4" s="62" t="str">
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="D4" s="62" t="str">
+        <x:v>Priority Read</x:v>
+      </x:c>
+      <x:c r="E4" s="62" t="str">
+        <x:v>Component Read</x:v>
+      </x:c>
+      <x:c r="F4" s="62" t="str">
+        <x:v>Municipal Pattern</x:v>
+      </x:c>
+      <x:c r="G4" s="62" t="str">
+        <x:v>Source Caveat</x:v>
+      </x:c>
+      <x:c r="H4" s="63" t="str">
+        <x:v>Planning Use</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="106.5" customHeight="1">
+      <x:c r="A5" s="64" t="str">
+        <x:v>Lanao del Sur</x:v>
+      </x:c>
+      <x:c r="B5" s="53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="53" t="str">
+        <x:v>Lanao del Sur has 17 LGUs in the dashboard source, 14 scored LGUs, and 407 facility records. The average composite score is 54.9/100, rank 1 of 4 in this snapshot.</x:v>
+      </x:c>
+      <x:c r="D5" s="53" t="str">
+        <x:v>Priority pressure is 84 high, 29 medium, and 6 low gaps. High-priority pressure equals 6.0 high gaps per scored LGU. Leading themes: Infrastructure, Immunization, Equipment, Referral, Governance.</x:v>
+      </x:c>
+      <x:c r="E5" s="53" t="str">
+        <x:v>Strongest component scores: HR Distribution 2.0 vs BARMM 2.0; Data Reporting 1.9 vs BARMM 1.9; Data Quality 1.8 vs BARMM 1.9. Weakest component scores: HR Density 0.2 vs BARMM 0.2; PhilHealth Status 0.4 vs BARMM 0.3; Cold Chain 0.7 vs BARMM 0.6. Above the embedded BARMM benchmark: Service Inventory (+0.3); Equipment Readiness (+0.2); PhilHealth Status (+0.1). Below the embedded BARMM benchmark: Data Quality (-0.1).</x:v>
+      </x:c>
+      <x:c r="F5" s="53" t="str">
+        <x:v>Highest scored LGUs: Buadiposo-Buntong (81.4); Marantao (73.9); Wao (58.8). Lower scored LGUs among scored records: Kapai (32.6); Masiu (43.7); Mulondo (44.0). Unscored LGU rows in source: Ditsaan-Ramain; Lanao del Sur; Tamparan.</x:v>
+      </x:c>
+      <x:c r="G5" s="53" t="str">
+        <x:v>Analysis overview reports broader facility coverage than the dashboard score source.</x:v>
+      </x:c>
+      <x:c r="H5" s="65" t="str">
+        <x:v>For follow-up, start with Infrastructure, Immunization, Equipment and the weakest component areas. Review the lower-scored LGUs before using this snapshot for resource prioritization. Reconcile the analysis-workbook facility count against the dashboard scoring inventory before treating facility totals as final.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="106.5" customHeight="1">
+      <x:c r="A6" s="66" t="str">
+        <x:v>Maguindanao del Norte</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="56" t="str">
+        <x:v>Maguindanao del Norte has 11 LGUs in the dashboard source, 11 scored LGUs, and 226 facility records. The average composite score is 53.3/100, rank 2 of 4 in this snapshot.</x:v>
+      </x:c>
+      <x:c r="D6" s="56" t="str">
+        <x:v>Priority pressure is 60 high, 22 medium, and 10 low gaps. High-priority pressure equals 5.5 high gaps per scored LGU. Leading themes: Immunization, Infrastructure, Equipment, Referral, Data Systems.</x:v>
+      </x:c>
+      <x:c r="E6" s="56" t="str">
+        <x:v>Strongest component scores: Data Quality 2.0 vs BARMM 1.9; Data Reporting 1.7 vs BARMM 1.9; Equipment Readiness 1.2 vs BARMM 1.3. Weakest component scores: HR Density 0.1 vs BARMM 0.2; PhilHealth Status 0.5 vs BARMM 0.3; Cold Chain 0.7 vs BARMM 0.6. Above the embedded BARMM benchmark: PhilHealth Status (+0.2); Cold Chain (+0.1); Data Quality (+0.1). Below the embedded BARMM benchmark: Service Inventory (-0.2); Data Reporting (-0.1); HR Density (-0.1).</x:v>
+      </x:c>
+      <x:c r="F6" s="56" t="str">
+        <x:v>Highest scored LGUs: Parang (90.0); Sultan Mastura (65.4); Sultan Kudarat (60.1). Lower scored LGUs among scored records: Cotabato City (36.9); Barira (44.9); Datu Blah T. Sinsuat (45.1). Unscored LGU rows in source: None in source.</x:v>
+      </x:c>
+      <x:c r="G6" s="56" t="str">
+        <x:v>Analysis overview reports broader facility coverage than the dashboard score source.</x:v>
+      </x:c>
+      <x:c r="H6" s="67" t="str">
+        <x:v>For follow-up, start with Immunization, Infrastructure, Equipment and the weakest component areas. Review the lower-scored LGUs before using this snapshot for resource prioritization. Reconcile the analysis-workbook facility count against the dashboard scoring inventory before treating facility totals as final.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="106.5" customHeight="1">
+      <x:c r="A7" s="66" t="str">
+        <x:v>Maguindanao del Sur</x:v>
+      </x:c>
+      <x:c r="B7" s="56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="56" t="str">
+        <x:v>Maguindanao del Sur has 2 LGUs in the dashboard source, 2 scored LGUs, and 36 facility records. The average composite score is 51.3/100, rank 3 of 4 in this snapshot.</x:v>
+      </x:c>
+      <x:c r="D7" s="56" t="str">
+        <x:v>Priority pressure is 8 high, 7 medium, and 1 low gaps. High-priority pressure equals 4.0 high gaps per scored LGU. Leading themes: HR, Infrastructure, Immunization, TB, Equipment.</x:v>
+      </x:c>
+      <x:c r="E7" s="56" t="str">
+        <x:v>Strongest component scores: Data Reporting 2.0 vs BARMM 1.9; Data Quality 2.0 vs BARMM 1.9; HR Distribution 2.0 vs BARMM 2.0. Weakest component scores: Cold Chain 0.1 vs BARMM 0.6; PhilHealth Status 0.1 vs BARMM 0.3; Equipment Readiness 0.5 vs BARMM 1.3. Above the embedded BARMM benchmark: HR Density (+0.3); Data Reporting (+0.1); Data Quality (+0.1). Below the embedded BARMM benchmark: Equipment Readiness (-0.8); Cold Chain (-0.5); Service Inventory (-0.3).</x:v>
+      </x:c>
+      <x:c r="F7" s="56" t="str">
+        <x:v>Highest scored LGUs: Datu Paglas (51.4); Shariff Aguak (51.3). Lower scored LGUs among scored records: Shariff Aguak (51.3); Datu Paglas (51.4). Unscored LGU rows in source: None in source.</x:v>
+      </x:c>
+      <x:c r="G7" s="56" t="str">
+        <x:v>No matching analysis overview file provided; dashboard source covers this province only.</x:v>
+      </x:c>
+      <x:c r="H7" s="67" t="str">
+        <x:v>For follow-up, start with HR, Infrastructure, Immunization and the weakest component areas. Review the lower-scored LGUs before using this snapshot for resource prioritization. Treat the MDS results as a partial source slice until the missing province analysis workbook or fuller dashboard source is added.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="106.5" customHeight="1">
+      <x:c r="A8" s="68" t="str">
+        <x:v>Special Geographic Area (SGA)</x:v>
+      </x:c>
+      <x:c r="B8" s="69" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="69" t="str">
+        <x:v>Special Geographic Area (SGA) has 8 LGUs in the dashboard source, 8 scored LGUs, and 66 facility records. The average composite score is 50.0/100, rank 4 of 4 in this snapshot.</x:v>
+      </x:c>
+      <x:c r="D8" s="69" t="str">
+        <x:v>Priority pressure is 47 high, 17 medium, and 1 low gaps. High-priority pressure equals 5.9 high gaps per scored LGU. Leading themes: Infrastructure, Equipment, Accreditation, Immunization, Governance.</x:v>
+      </x:c>
+      <x:c r="E8" s="69" t="str">
+        <x:v>Strongest component scores: Data Reporting 2.0 vs BARMM 1.9; Data Quality 1.9 vs BARMM 1.9; Equipment Readiness 1.2 vs BARMM 1.3. Weakest component scores: PhilHealth Status 0.0 vs BARMM 0.3; HR Density 0.3 vs BARMM 0.2; Cold Chain 0.4 vs BARMM 0.6. Above the embedded BARMM benchmark: Data Reporting (+0.1); HR Density (+0.1). Below the embedded BARMM benchmark: PhilHealth Status (-0.3); Cold Chain (-0.2); Service Inventory (-0.2).</x:v>
+      </x:c>
+      <x:c r="F8" s="69" t="str">
+        <x:v>Highest scored LGUs: Kapalawan (57.1); Nabalawag (57.1); Ligawasan (54.1). Lower scored LGUs among scored records: Pahamuddin (33.3); Tugunan (44.4); Old Kaabakan (50.0). Unscored LGU rows in source: None in source.</x:v>
+      </x:c>
+      <x:c r="G8" s="69" t="str">
+        <x:v>Analysis overview reports broader facility coverage than the dashboard score source.</x:v>
+      </x:c>
+      <x:c r="H8" s="70" t="str">
+        <x:v>For follow-up, start with Infrastructure, Equipment, Accreditation and the weakest component areas. Review the lower-scored LGUs before using this snapshot for resource prioritization. Reconcile the analysis-workbook facility count against the dashboard scoring inventory before treating facility totals as final.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="17.219999313354492" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28.889999389648438" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.5600004196167" hidden="0" customWidth="1"/>
@@ -3085,7 +3263,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4686,7 +4864,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4934,11 +5112,11 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b733365d658425a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra383467b121543f7"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5157,7 +5335,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
